--- a/naver-place-crawler/results_health/춘천_PT.xlsx
+++ b/naver-place-crawler/results_health/춘천_PT.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="49" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>아베크짐</t>
+          <t>강북짐</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>wannabe-pt@naver.com</t>
+          <t>lvhr@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1340-0660</t>
+          <t>033-244-2445</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>강원 춘천시 춘천로17번길 31 3층 301호,302호</t>
+          <t>강원특별자치도 춘천시 영서로 2938 101호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sFMuVPdh</t>
+          <t>https://talk.naver.com/ct/wzg62j9#nafullscreen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -611,27 +611,27 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zpx4</t>
+          <t>https://talk.naver.com/ct/wzg62j9</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="Q2" t="n">
-        <v>356</v>
+        <v>19</v>
       </c>
       <c r="R2" t="n">
-        <v>412</v>
+        <v>33</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1147379761</t>
+          <t>1326203426</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1147379761</t>
+          <t>https://m.place.naver.com/place/1326203426</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>렉슬프로짐</t>
+          <t>메이크바디</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rexleprogym@naver.com</t>
+          <t>makeabody1@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1442-9688</t>
+          <t>033-263-1331</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>강원 춘천시 안마산로 107-1 B1층 102호</t>
+          <t>강원특별자치도 춘천시 퇴계로93번길 15</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rexleprogym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,24 +694,20 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w7k39ti</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,17 +715,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1503</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>1555</v>
+        <v>1</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1421522019</t>
+          <t>894060199</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1421522019</t>
+          <t>https://m.place.naver.com/place/894060199</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -755,34 +751,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>올핀트레이닝센터</t>
+          <t>제트짐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>yodavely@naver.com</t>
+          <t>lastnameischoii@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>033-910-0340</t>
+          <t>033-242-7780</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원 춘천시 경춘로 2354 7층 701호</t>
+          <t>강원특별자치도 춘천시 동면 만천로 57-1 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/allinone_infinity</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,7 +788,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -813,17 +809,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>114</v>
+        <v>2</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1367250279</t>
+          <t>2033455292</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1367250279</t>
+          <t>https://m.place.naver.com/place/2033455292</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -849,34 +845,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>고고PT&amp;WOMEN</t>
+          <t>퍼스트짐PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gogo_pt2@naver.com</t>
+          <t>tynsongdo12@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1378-2924</t>
+          <t>0507-1314-2310</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>강원 춘천시 남춘로36번길 20 2층(퇴계동)</t>
+          <t>강원특별자치도 춘천시 동광길 1 장보고빌딩2층 퍼스트짐</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gogo_pt2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -886,12 +882,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -907,17 +903,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="Q5" t="n">
-        <v>128</v>
+        <v>19</v>
       </c>
       <c r="R5" t="n">
-        <v>156</v>
+        <v>35</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,12 +922,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1893842305</t>
+          <t>1907142016</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1893842305</t>
+          <t>https://m.place.naver.com/place/1907142016</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -943,34 +939,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>고고PT&amp;헬스</t>
+          <t>플렉스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gogo_pt@naver.com</t>
+          <t>rlatkdduq884@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1314-2924</t>
+          <t>0507-1413-4914</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강원 춘천시 안마산로 97 3층 고고피티</t>
+          <t>강원특별자치도 춘천시 후석로 43 5층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gogo_pt</t>
+          <t>https://blog.naver.com/rlatkdduq884</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1001,17 +997,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>175</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
-        <v>322</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>497</v>
+        <v>8</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1020,12 +1016,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1719180960</t>
+          <t>1142026957</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1719180960</t>
+          <t>https://m.place.naver.com/place/1142026957</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1037,34 +1033,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>이즈원 필라테스</t>
+          <t>HK GYM 후평점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>napilates-yina@naver.com</t>
+          <t>sungminjin1004@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1497-2241</t>
+          <t>0507-1331-0739</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>강원 춘천시 영서로 2347-1 2층</t>
+          <t>강원특별자치도 춘천시 보안길 61 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/napilates-yina/224230819363</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1074,24 +1070,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5vzdd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1099,17 +1091,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="Q7" t="n">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="R7" t="n">
-        <v>194</v>
+        <v>43</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1118,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1888353200</t>
+          <t>1417516201</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1888353200</t>
+          <t>https://m.place.naver.com/place/1417516201</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1135,34 +1127,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>노프짐 춘천점</t>
+          <t>머슬핏P.T</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>noffgym@naver.com</t>
+          <t>whwnsdud8914@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1305-1277</t>
+          <t>0507-1418-5616</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원 춘천시 동내면 춘천순환로 63 명일빌딩 3층 노프짐</t>
+          <t>강원특별자치도 춘천시 영서로 2790 2, 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/noffgym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1172,24 +1164,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42pbe</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1197,17 +1185,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>146</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>312</v>
+        <v>4</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1931931002</t>
+          <t>1163021653</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1931931002</t>
+          <t>https://m.place.naver.com/place/1163021653</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1238,91 +1226,8237 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>헬스 &amp; PT 굿리프트</t>
+          <t>코어&amp;밸런스트레이닝센터</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>goodlift_hong@naver.com</t>
+          <t>kth38900@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1441-6464</t>
+          <t>0507-1341-3855</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원 춘천시 효석로 37 1층</t>
+          <t>강원특별자치도 춘천시 행촌로 29 6층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>https://blog.naver.com/kth38900</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>98</v>
+      </c>
+      <c r="R9" t="n">
+        <v>131</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1045913410</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1045913410</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>시크릿피티스튜디오 우두점</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>sz4337@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1309-0611</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 충열로16번길 22-2 1층</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sz4337</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>22</v>
+      </c>
+      <c r="R10" t="n">
+        <v>70</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1569852438</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1569852438</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>올핀트레이닝센터</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>yodavely@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>033-910-0340</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 경춘로 2354 7층 701호</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/allinone_infinity</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>40</v>
+      </c>
+      <c r="R11" t="n">
+        <v>114</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1367250279</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1367250279</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>렉슬휘트니스 헬스&amp;PT 우두점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>rexlefitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1403-3725</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 충열로 45 6층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rexlefitness/</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>111</v>
+      </c>
+      <c r="R12" t="n">
+        <v>189</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>36651112</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36651112</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>위캔방문운동센터 강원도지점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>dongwoo8@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1877-4160</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 충혼길52번길 10 드림타워 3층 303호 제10호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dongwoo8</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>86</v>
+      </c>
+      <c r="R13" t="n">
+        <v>86</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1541516692</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1541516692</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>근육터짐</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>hotdogto@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1334-5943</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 후석로 42 3층</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>13</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2069895660</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2069895660</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>렉슬프로짐</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>rexleprogym@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1442-9688</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 안마산로 107-1 B1층 102호</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rexleprogym</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>1503</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>52</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1555</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1421522019</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1421522019</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>고고PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>gogo_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1314-2924</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 안마산로 97 3층 고고피티</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gogo_pt</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>322</v>
+      </c>
+      <c r="R16" t="n">
+        <v>497</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1719180960</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1719180960</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>더바디랩PT&amp;필라테스 춘천점</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>thebodylabcc@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 퇴계농공로 22 프라임타워 4층 더바디랩PT&amp;필라테스 춘천점</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/thebodylabcc/223438996483</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>69</v>
+      </c>
+      <c r="R17" t="n">
+        <v>136</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1928947972</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1928947972</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>다이어트,비만</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>에소코핏 춘천퇴계점</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>essocofit25@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1320-0034</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 김유정로 1864 2층 201호 에소코핏 춘천퇴계점</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/essoco_fit?igsh=MWVsNWkweGd1cGw1bA==</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>174</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>159</v>
+      </c>
+      <c r="R18" t="n">
+        <v>333</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1106708590</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1106708590</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>춘천 바디앤라이프 필라테스 &amp; PT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>bodynlife_@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1402-3651</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 영서로 2323 3층</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>http://www.bodynlife.co.kr/</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>168</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>107</v>
+      </c>
+      <c r="R19" t="n">
+        <v>275</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1183939962</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1183939962</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>득근짐헬스PT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>noffgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1321-7186</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 동내면 거두택지길 87-16 3층</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>48</v>
+      </c>
+      <c r="R20" t="n">
+        <v>59</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1216280851</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1216280851</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>프로핏짐 헬스 PT 바레 기구필라테스</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>progym01@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1408-5002</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 시청길 32 해찬빌딩 5층</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://naver.me/5pN0h5wi</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>335</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>205</v>
+      </c>
+      <c r="R21" t="n">
+        <v>540</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1624505512</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1624505512</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>언니PT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>handalsalgii@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1340-8594</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 세실로 267 2층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>http://instagram.com/unni_pt2020</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>11</v>
+      </c>
+      <c r="R22" t="n">
+        <v>78</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1534419390</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1534419390</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>바디블룸</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>healer_choi_j@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1388-7923</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 서부대성로47번길 10 비아문하우스 3층</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>http://bodybloom.kr/</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>88</v>
+      </c>
+      <c r="R23" t="n">
+        <v>96</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1787539511</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1787539511</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>휘트니스플러스</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>jys9347@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1400-8432</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 서부대성로239번길 21 미래빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jys9347</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>407</v>
+      </c>
+      <c r="R24" t="n">
+        <v>434</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>37921870</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37921870</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>갈라짐</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>galagym@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 퇴계로 247 1층</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gala_gym2025</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>119</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>28</v>
+      </c>
+      <c r="R25" t="n">
+        <v>147</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>2052131177</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2052131177</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>브이핏 온의점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>v-fit_onui@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1405-1594</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 스포츠타운길 494 3층 301호</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/v.fit_vv</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>27</v>
+      </c>
+      <c r="R26" t="n">
+        <v>77</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1141962685</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1141962685</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>태닝</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>잇츠탠 춘천 퇴계점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>chosy91@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1415-1092</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 영서로 2153 . 2층 (중간)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/chosy91</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>41</v>
+      </c>
+      <c r="R27" t="n">
+        <v>136</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1110458840</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1110458840</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>제이케이짐거두점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>jkgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>033-264-0096</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 동내면 공지로 76 벽진빌딩 6층</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jk_gym82</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>252</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>164</v>
+      </c>
+      <c r="R28" t="n">
+        <v>416</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>37871059</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37871059</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>바디니즈</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>bodyneeds@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1390-6532</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 퇴계로 249 3층 바디니즈</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bodyneeds</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>263</v>
+      </c>
+      <c r="R29" t="n">
+        <v>296</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1124795045</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1124795045</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>스타휘트니스</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>muscleiron@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>033-244-2277</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 퇴계로105번길 5 지효빌딩5층</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/star_fitness_pt</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>339</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>21</v>
+      </c>
+      <c r="R30" t="n">
+        <v>360</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>15095525</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/15095525</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>시크릿피티스튜디오 석사점</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ccp1018@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1339-2058</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 후석로45번길 42 1층</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ccp1018</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4</v>
+      </c>
+      <c r="R31" t="n">
+        <v>46</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1243260621</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1243260621</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>GYM90</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>gym_90@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1436-6321</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 우두1길 157 1동 2층 전체호</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>215</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>7</v>
+      </c>
+      <c r="R32" t="n">
+        <v>222</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1680400155</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1680400155</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>RS휘트니스</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>realsfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1489-6684</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 후석로 361 토우사우나 2층 RS휘트니스</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/realsfitness</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>79</v>
+      </c>
+      <c r="R33" t="n">
+        <v>110</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1089459848</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1089459848</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>고고PT&amp;WOMEN</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>gogo_pt2@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1378-2924</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 남춘로36번길 20 2층(퇴계동)</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gogo_pt2</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>128</v>
+      </c>
+      <c r="R34" t="n">
+        <v>156</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1893842305</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1893842305</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>원퍼포먼스짐</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>won_performance_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1407-9299</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 방송길 77 지하1층 108호</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/won_performance_gym</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>38</v>
+      </c>
+      <c r="R35" t="n">
+        <v>85</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1547043602</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1547043602</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>올라운더피트니스</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>leedydrud1@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>033-241-2003</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 후석로 246 3층</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>184</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>184</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1406326621</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1406326621</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>골목PT</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>altjs1298@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1384-8510</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 춘천로255번길 6 202호</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>http://gmpt.co.kr</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>155</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>48</v>
+      </c>
+      <c r="R37" t="n">
+        <v>203</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1416396652</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1416396652</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>핏불짐</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>pitbullgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1498-3224</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 충열로 32 유치원동</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/pitbullgym</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wy2vieq</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>20</v>
+      </c>
+      <c r="R38" t="n">
+        <v>67</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>34053109</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34053109</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>파리휘트니스</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>myellowgreen@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 춘천로 204</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/paris__fitness</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>23</v>
+      </c>
+      <c r="R39" t="n">
+        <v>50</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>504638622</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/504638622</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>썬더짐</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>hth8307@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1311-9764</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 동내면 영서로 1745-7 썬더짐</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thundergym_official</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>1948</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>80</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2028</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1875414500</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1875414500</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>노벨짐 석사점</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>sodkwk@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1382-7834</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 지석로 85 강남프라자 4층</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sodkwk</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>380</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>471</v>
+      </c>
+      <c r="R41" t="n">
+        <v>851</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2076990312</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2076990312</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>운동시간</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>so_younique@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1386-4967</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 우두1길 79 1층</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>147</v>
+      </c>
+      <c r="R42" t="n">
+        <v>147</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1012519309</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1012519309</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>익투스짐 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ichthus_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1352-9469</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 동내면 춘천순환로 134 MS TOWER 3층</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ichthus_gym</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>17</v>
+      </c>
+      <c r="R43" t="n">
+        <v>38</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1360432944</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1360432944</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>저스트원짐</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>justone_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>033-263-0708</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 김유정로 1891 3층 저스트원짐</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/justone_gym</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>213</v>
+      </c>
+      <c r="R44" t="n">
+        <v>348</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1643330885</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1643330885</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>제이케이짐 헬스&amp;PT 우두점</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>hipster58@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1409-9682</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 우두1길 31 2층 201호, 202호 3층 301호, 302호</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jkgym0096?igsh=MWgxaHF4dXNibXp0Zw==</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>415</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>41</v>
+      </c>
+      <c r="R45" t="n">
+        <v>456</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1020118945</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1020118945</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>어드밴스짐</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>anyfitadvance@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 퇴계로 92 수빌딩 2층~5층 어드밴스짐</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/anyfitadvance</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>164</v>
+      </c>
+      <c r="R46" t="n">
+        <v>236</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1641018455</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1641018455</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>더 피트니스랩 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>choee93@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1348-7053</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 공지로 388 2층</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thefitnesslab_yaksa?igsh=ZjByaWc0cGMxdXZt&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>361</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>37</v>
+      </c>
+      <c r="R47" t="n">
+        <v>398</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1110542863</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1110542863</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>에스휘트니스</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>sfitness_@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>033-256-8899</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 행촌로 27 B1층</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sfitness_</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>189</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>135</v>
+      </c>
+      <c r="R48" t="n">
+        <v>324</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1383952554</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1383952554</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>헬스 &amp; PT 굿리프트</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>goodlift_hong@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1441-6464</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 효석로 37 1층</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>https://smartstore.naver.com/goodlift_cc</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wpxy8r2</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
         <v>68</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q49" t="n">
         <v>37</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R49" t="n">
         <v>105</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
         <is>
           <t>1966374826</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1966374826</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>국민헬스 학곡리점</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>namhun1234@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1429-2533</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 동내면 영서로 1781 2층</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/km_health1</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2</v>
+      </c>
+      <c r="R50" t="n">
+        <v>135</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1702373214</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1702373214</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>바디로</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>body-ro@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1317-0425</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 서부대성로48번길 12 2~4층</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/body__ro</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>11</v>
+      </c>
+      <c r="R51" t="n">
+        <v>12</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1236135124</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1236135124</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>포나인필라테스 애막골점</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>four9_pilates@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1469-9920</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 후석로186번길 18 3층</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://litt.ly/four9pilates</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>178</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>17</v>
+      </c>
+      <c r="R52" t="n">
+        <v>195</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1234778058</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1234778058</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>늘필라테스</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>neulpilates13@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1387-8870</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 우두1길 87 더클래스 102호 늘필라테스_pt</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>http://open.kakao.com/o/sfEVP7xf</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>10</v>
+      </c>
+      <c r="R53" t="n">
+        <v>44</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1771319026</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1771319026</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>베네핏휘트니스</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>dldbfla0629@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1366-5583</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 김유정로 1852-35 4층</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bene_fit__official/</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>24</v>
+      </c>
+      <c r="R54" t="n">
+        <v>108</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1359593316</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1359593316</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>아베크짐</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>wannabe-pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1340-0660</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 춘천로17번길 31 3층 301호,302호</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sFMuVPdh</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>356</v>
+      </c>
+      <c r="R55" t="n">
+        <v>412</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1147379761</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1147379761</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>에스핏 춘천점</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>kdhonepick@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 동내면 춘천순환로 130 3층 에스핏</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sfit_se_a</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>51</v>
+      </c>
+      <c r="R56" t="n">
+        <v>134</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1412719700</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1412719700</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>미드나잇 짐 온의점</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>allow18587@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1421-3525</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 춘천로17번길 21 춘천강남하이엔드 2층 206호</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jang_ji_won_/</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" t="n">
+        <v>54</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1986587948</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1986587948</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>카페인헬스장</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>skykjy87@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1429-3038</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 스무숲길 1 201호</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>4</v>
+      </c>
+      <c r="R58" t="n">
+        <v>4</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1045651944</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1045651944</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>이뻐짐 [E4GYM]</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>mim_n_@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>033-253-2627</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 중앙로 41-1 2층 E4GYM</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/e_4_gym_1222</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>6</v>
+      </c>
+      <c r="R59" t="n">
+        <v>17</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1638116827</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1638116827</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>잭슨나인스 휘트니스</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>khyjkj3120@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1315-0739</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 중앙로 193 2층</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>9</v>
+      </c>
+      <c r="R60" t="n">
+        <v>19</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1972339696</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1972339696</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>노프짐 춘천점</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>noffgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1305-1277</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 동내면 춘천순환로 63 명일빌딩 3층 노프짐</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/noffgym</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>166</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>146</v>
+      </c>
+      <c r="R61" t="n">
+        <v>312</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1931931002</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1931931002</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>바디팩토리</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>black3927@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1354-5664</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 우석로38번길 133 1층</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/black3927</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>27</v>
+      </c>
+      <c r="R62" t="n">
+        <v>31</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1474544377</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1474544377</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>카페</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>바디블룸피트니스카페</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>u_yong@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1347-7051</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 서부대성로47번길 14 2층</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bodybloom_fitness_cafe?igsh=ZzlpaHdtMXAwN3Zh&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>9</v>
+      </c>
+      <c r="R63" t="n">
+        <v>20</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1051475106</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1051475106</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>디엔에스짐</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>primitive3965@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1335-8796</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 만천로 239 3층</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dns_gym_?igsh=cm9sMXM3bHUzeGM%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" t="n">
+        <v>38</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>2098038105</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2098038105</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>고릴라 트레이닝</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>cp2261@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 퇴계로 242 (석사동, 퇴계(4)주공아파트) 406동 404호</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1691417797</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1691417797</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>머슬핏휘트니스 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ekrodsyd1@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1316-5577</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 후석로 314 2층</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/team_musclefit_?igsh=MXM4MzR0N2NuMDBydQ==</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>375</v>
+      </c>
+      <c r="R66" t="n">
+        <v>551</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1880702102</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1880702102</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>비포앤애프터짐</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>beforeaftergym@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1409-0099</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 동면 춘천순환로 613 청일빌딩 7층</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/beforeaftergym</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>314</v>
+      </c>
+      <c r="R67" t="n">
+        <v>326</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>73801545</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/73801545</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>가설재비티아시바피티아시바파이프유로폼임대대여설치</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>rodtmdu12@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>070-8084-7471</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 교동</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>1</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1646138658</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1646138658</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>토익</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>심재영 어학원</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>jaycma@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1331-5505</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 애막골길20번길 51 1층</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jaycma</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>3</v>
+      </c>
+      <c r="R69" t="n">
+        <v>28</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>36329366</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36329366</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>바디애 석사점</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>body__love@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>033-261-9682</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 퇴계로 181 2층</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/body__love</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>318</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>141</v>
+      </c>
+      <c r="R70" t="n">
+        <v>459</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1555187997</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1555187997</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>엘알엠 트레이닝</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>lrmtraining@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1335-2075</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 영서로 2670-1 3층 엘알엠 트레이닝</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/lrmtraining</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>217</v>
+      </c>
+      <c r="R71" t="n">
+        <v>255</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1702068915</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1702068915</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>연세 레하 재활운동센터 &amp; 건강운동 센터 본점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>kys544@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1369-5445</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 방송길 77 춘천센트럴 타워 푸르지오 상가 2층 2249호</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://rehabe.co.kr</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>226</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>229</v>
+      </c>
+      <c r="R72" t="n">
+        <v>455</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1657852472</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1657852472</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>브이핏</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>v-fit_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1354-1394</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 백령로 214 2층</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/v.fit_v</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>60</v>
+      </c>
+      <c r="R73" t="n">
+        <v>206</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1219020937</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1219020937</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>H휘트니스</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>hyunsunnn@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>033-244-1225</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 영서로 2333 3층</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Hfitness1225/</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>3</v>
+      </c>
+      <c r="R74" t="n">
+        <v>12</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>397674688</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/397674688</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>청년헬스 석사점</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>youngmanhelth_seoksa@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1379-7305</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 퇴계농공로 19 1동 3층 301호 청년헬스 석사점</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>4</v>
+      </c>
+      <c r="R75" t="n">
+        <v>23</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1300891309</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1300891309</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>리즌피트니스</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>hoyoungbum@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1315-7737</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 퇴계로145번길 7-14 1층</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.ipbf.co.kr/news/articleView.html?idxno=1168</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>37</v>
+      </c>
+      <c r="R76" t="n">
+        <v>168</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1687011602</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1687011602</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>프리짐 강대정문점</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>honeytip111@naver.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0507-1411-5058</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 백령로 19 3층 프리짐</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>8</v>
+      </c>
+      <c r="R77" t="n">
+        <v>13</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>1169711652</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1169711652</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>청년헬스 온의점</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>chuncheon_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0507-1495-7447</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 스포츠타운길 533 4층 청년헬스 온의점</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/youngmanhealth_onui/</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>40</v>
+      </c>
+      <c r="R78" t="n">
+        <v>49</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>1525752804</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1525752804</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>국민헬스 퇴계점</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>sh5351a@naver.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 안마산로 219 2층 국민헬스</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/km_health2</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>5</v>
+      </c>
+      <c r="R79" t="n">
+        <v>13</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>1056554675</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1056554675</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>합창단</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>세렌디피티</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>reddevil857@naver.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0507-1338-7088</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 우두1길 140 202동 1501호</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@Serendipity-Choir</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>1</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>1506763332</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1506763332</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>씨에스짐</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>csgym114@naver.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0507-1347-6320</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 세실로 114 2층</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/csgym114</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc0i3i</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>115</v>
+      </c>
+      <c r="R81" t="n">
+        <v>465</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>1180314397</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1180314397</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>점핑 우두</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>s-body_@naver.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0507-1469-1745</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 사우벌길 61 2층 202호</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jumping_chuncheon</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>1</v>
+      </c>
+      <c r="R82" t="n">
+        <v>1</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>2032914433</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2032914433</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>브레이브힐 사농점</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2014bravehill@naver.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1342-5155</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 사우4길 36 3층</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>http://bravehill2014.com/</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>112</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>35</v>
+      </c>
+      <c r="R83" t="n">
+        <v>147</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>1933437118</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1933437118</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>서울가설재BT비티아시바PT피티아시바파이프비계임대시공판매</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>070-8040-8904</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 교동</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>3</v>
+      </c>
+      <c r="R84" t="n">
+        <v>3</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>1172148715</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1172148715</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>봄날의헬스클럽</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>jjubika1@naver.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0507-1485-1213</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 근화길15번길 23 3층</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/springday0313</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>5</v>
+      </c>
+      <c r="R85" t="n">
+        <v>10</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>1878331023</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1878331023</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>바디디자인 PT 소양점</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>sarangel_@naver.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0507-1421-8049</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 서부대성로 12 신동아아파트 3층 38호</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>86</v>
+      </c>
+      <c r="R86" t="n">
+        <v>120</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>1215772042</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1215772042</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>청년헬스 한림대점</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>youngpeoplehealth@naver.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0507-1346-7305</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 삭주로 80 2, 3층 청년헬스 한림대점</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/youngpeoplehealth</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>132</v>
+      </c>
+      <c r="R87" t="n">
+        <v>154</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>1011748353</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1011748353</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>머슬메이드</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>golfarm@naver.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 서부대성로 247 3층</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/musle_made_chuncheon?igsh=MXcwemV5N3RqOTdlcQ%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>2</v>
+      </c>
+      <c r="R88" t="n">
+        <v>9</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>1748574167</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1748574167</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>워밸짐PT</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>gustnrla77@naver.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1354-3979</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 동면 만천양지길 45 1층 워밸짐</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gustnrla77</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>47</v>
+      </c>
+      <c r="R89" t="n">
+        <v>52</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>1371922355</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1371922355</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>밤새헬스</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>qkatogpftm222@naver.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0507-1303-4485</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 남춘로36번길 75 1층</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/qkatogpftm222</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>113</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>13</v>
+      </c>
+      <c r="R90" t="n">
+        <v>126</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>1338361534</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1338361534</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>윌앤바디</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ccp1018@naver.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0507-1384-1780</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 영서로 2347-1 3층</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_JSrzX</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>3</v>
+      </c>
+      <c r="R91" t="n">
+        <v>17</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>2021095397</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2021095397</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>바디애 후평점</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>body__love@naver.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>033-254-8227</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 후석로 326 엠타워 8층</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fitness_bodylove/</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>495</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>98</v>
+      </c>
+      <c r="R92" t="n">
+        <v>593</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>1046174224</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1046174224</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>체육관</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>원팀레슬링</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>oneteam-wrestling@naver.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 영서로 2153 4층</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oneteam1987</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>1</v>
+      </c>
+      <c r="R93" t="n">
+        <v>1</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>1962319601</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1962319601</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>여성전용피티샵 루피티</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ksr168@naver.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0507-1332-9062</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 우석로4번길 61 1층</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ksr168</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>21</v>
+      </c>
+      <c r="R94" t="n">
+        <v>49</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>1700884879</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1700884879</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>PT버프</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>haeeeun12@naver.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0507-1393-8267</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 우두6길 5 2층(우두동)</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>8</v>
+      </c>
+      <c r="R95" t="n">
+        <v>23</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>1759013791</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1759013791</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>밸류PT&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>mpc111@naver.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>033-263-9902</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>강원특별자치도 춘천시 퇴계농공로 20 301호</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://valuablelife.kr/</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>716</v>
+      </c>
+      <c r="R96" t="n">
+        <v>856</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>1742966330</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1742966330</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>

--- a/naver-place-crawler/results_health/춘천_PT.xlsx
+++ b/naver-place-crawler/results_health/춘천_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="33" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1518</v>
+        <v>1525</v>
       </c>
       <c r="Q3" t="n">
         <v>52</v>
       </c>
       <c r="R3" t="n">
-        <v>1570</v>
+        <v>1577</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -756,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>아베크짐</t>
+          <t>여성전용피티샵 루피티</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>wannabe-pt@naver.com</t>
+          <t>ksr168@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1340-0660</t>
+          <t>0507-1332-9062</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원 춘천시 춘천로17번길 31 3층 301호,302호</t>
+          <t>강원 춘천시 우석로4번길 61 1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sFMuVPdh</t>
+          <t>https://blog.naver.com/ksr168</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zpx4</t>
+          <t>https://talk.naver.com/ct/w46qai</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Q4" t="n">
-        <v>407</v>
+        <v>21</v>
       </c>
       <c r="R4" t="n">
-        <v>463</v>
+        <v>49</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1147379761</t>
+          <t>1700884879</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1147379761</t>
+          <t>https://m.place.naver.com/place/1700884879</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -854,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>여성전용피티샵 루피티</t>
+          <t>아베크짐</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ksr168@naver.com</t>
+          <t>wannabe-pt@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1332-9062</t>
+          <t>0507-1340-0660</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>강원 춘천시 우석로4번길 61 1층</t>
+          <t>강원 춘천시 춘천로17번길 31 3층 301호,302호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ksr168</t>
+          <t>https://open.kakao.com/o/sFMuVPdh</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w46qai</t>
+          <t>https://talk.naver.com/ct/w5zpx4</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="Q5" t="n">
-        <v>21</v>
+        <v>413</v>
       </c>
       <c r="R5" t="n">
-        <v>49</v>
+        <v>469</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1700884879</t>
+          <t>1147379761</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1700884879</t>
+          <t>https://m.place.naver.com/place/1147379761</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1034,41 +1034,41 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>이즈원 필라테스</t>
+          <t>노프짐 춘천점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>napilates-yina@naver.com</t>
+          <t>noffgym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1497-2241</t>
+          <t>0507-1305-1277</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>강원 춘천시 영서로 2347-1 2층</t>
+          <t>강원 춘천시 동내면 춘천순환로 63 명일빌딩 3층 노프짐</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/napilates-yina/224230819363</t>
+          <t>https://blog.naver.com/noffgym</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5vzdd</t>
+          <t>https://talk.naver.com/ct/w42pbe</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>125</v>
+        <v>168</v>
       </c>
       <c r="Q7" t="n">
-        <v>73</v>
+        <v>147</v>
       </c>
       <c r="R7" t="n">
-        <v>198</v>
+        <v>315</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,17 +1122,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1888353200</t>
+          <t>1931931002</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1888353200</t>
+          <t>https://m.place.naver.com/place/1931931002</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1144,29 +1144,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>노프짐 춘천점</t>
+          <t>헬스 &amp; PT 굿리프트</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>noffgym@naver.com</t>
+          <t>goodlift_hong@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1305-1277</t>
+          <t>0507-1441-6464</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원 춘천시 동내면 춘천순환로 63 명일빌딩 3층 노프짐</t>
+          <t>강원 춘천시 효석로 37 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/noffgym</t>
+          <t>https://smartstore.naver.com/goodlift_cc</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42pbe</t>
+          <t>https://talk.naver.com/ct/wpxy8r2</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>168</v>
+        <v>70</v>
       </c>
       <c r="Q8" t="n">
-        <v>147</v>
+        <v>38</v>
       </c>
       <c r="R8" t="n">
-        <v>315</v>
+        <v>108</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,51 +1220,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1931931002</t>
+          <t>1966374826</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1931931002</t>
+          <t>https://m.place.naver.com/place/1966374826</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>헬스 &amp; PT 굿리프트</t>
+          <t>엘알엠 트레이닝</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>goodlift_hong@naver.com</t>
+          <t>lrmtraining@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1441-6464</t>
+          <t>0507-1335-2075</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원 춘천시 효석로 37 1층</t>
+          <t>강원 춘천시 영서로 2670-1 3층 엘알엠 트레이닝</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/goodlift_cc</t>
+          <t>https://blog.naver.com/lrmtraining</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wpxy8r2</t>
+          <t>https://talk.naver.com/ct/w4enem</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="Q9" t="n">
-        <v>37</v>
+        <v>219</v>
       </c>
       <c r="R9" t="n">
-        <v>107</v>
+        <v>257</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,115 +1318,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1966374826</t>
+          <t>1702068915</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1966374826</t>
+          <t>https://m.place.naver.com/place/1702068915</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>엘알엠 트레이닝</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>lrmtraining@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1335-2075</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>강원 춘천시 영서로 2670-1 3층 엘알엠 트레이닝</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/lrmtraining</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4enem</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>219</v>
-      </c>
-      <c r="R10" t="n">
-        <v>257</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1702068915</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1702068915</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/춘천_PT.xlsx
+++ b/naver-place-crawler/results_health/춘천_PT.xlsx
@@ -918,10 +918,10 @@
         <v>56</v>
       </c>
       <c r="Q5" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="R5" t="n">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/춘천_PT.xlsx
+++ b/naver-place-crawler/results_health/춘천_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1525</v>
+        <v>1528</v>
       </c>
       <c r="Q3" t="n">
         <v>52</v>
       </c>
       <c r="R3" t="n">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -1327,6 +1327,100 @@
         </is>
       </c>
       <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>더바디랩PT&amp;필라테스 춘천점</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>thebodylabcc@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>강원 춘천시 퇴계농공로 22 프라임타워 4층 더바디랩PT&amp;필라테스 춘천점</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/thebodylabcc/223438996483</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4g6fm</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>69</v>
+      </c>
+      <c r="R10" t="n">
+        <v>136</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1928947972</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1928947972</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/춘천_PT.xlsx
+++ b/naver-place-crawler/results_health/춘천_PT.xlsx
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1528</v>
+        <v>1531</v>
       </c>
       <c r="Q3" t="n">
         <v>52</v>
       </c>
       <c r="R3" t="n">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -918,10 +918,10 @@
         <v>56</v>
       </c>
       <c r="Q5" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="R5" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/춘천_PT.xlsx
+++ b/naver-place-crawler/results_health/춘천_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>강원 춘천시 경춘로 2354 7층 701호</t>
+          <t>강원특별자치도 춘천시 경춘로 2354 7층 701호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>강원 춘천시 안마산로 107-1 B1층 102호</t>
+          <t>강원특별자치도 춘천시 안마산로 107-1 B1층 102호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w7k39ti</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -744,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -773,7 +769,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원 춘천시 우석로4번길 61 1층</t>
+          <t>강원특별자치도 춘천시 우석로4번길 61 1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -798,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46qai</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -842,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -871,7 +863,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>강원 춘천시 춘천로17번길 31 3층 301호,302호</t>
+          <t>강원특별자치도 춘천시 춘천로17번길 31 3층 301호,302호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -896,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5zpx4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>O</t>
@@ -918,10 +906,10 @@
         <v>56</v>
       </c>
       <c r="Q5" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="R5" t="n">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -940,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -969,7 +957,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강원 춘천시 남춘로36번길 20 2층(퇴계동)</t>
+          <t>강원특별자치도 춘천시 남춘로36번길 20 2층(퇴계동)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1034,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1051,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>강원 춘천시 동내면 춘천순환로 63 명일빌딩 3층 노프짐</t>
+          <t>강원특별자치도 춘천시 동내면 춘천순환로 63 명일빌딩 3층 노프짐</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1088,14 +1076,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42pbe</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1132,7 +1116,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1145,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원 춘천시 효석로 37 1층</t>
+          <t>강원특별자치도 춘천시 효석로 37 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1186,14 +1170,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wpxy8r2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1230,7 +1210,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1239,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원 춘천시 영서로 2670-1 3층 엘알엠 트레이닝</t>
+          <t>강원특별자치도 춘천시 영서로 2670-1 3층 엘알엠 트레이닝</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1284,14 +1264,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4enem</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1328,101 +1304,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>더바디랩PT&amp;필라테스 춘천점</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>thebodylabcc@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>강원 춘천시 퇴계농공로 22 프라임타워 4층 더바디랩PT&amp;필라테스 춘천점</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/thebodylabcc/223438996483</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4g6fm</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>67</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>69</v>
-      </c>
-      <c r="R10" t="n">
-        <v>136</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1928947972</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1928947972</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/춘천_PT.xlsx
+++ b/naver-place-crawler/results_health/춘천_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>강원특별자치도 춘천시 경춘로 2354 7층 701호</t>
+          <t>강원 춘천시 경춘로 2354 7층 701호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -675,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>강원특별자치도 춘천시 안마산로 107-1 B1층 102호</t>
+          <t>강원 춘천시 안마산로 107-1 B1층 102호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +700,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w7k39ti</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -769,7 +773,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원특별자치도 춘천시 우석로4번길 61 1층</t>
+          <t>강원 춘천시 우석로4번길 61 1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +798,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46qai</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -863,7 +871,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>강원특별자치도 춘천시 춘천로17번길 31 3층 301호,302호</t>
+          <t>강원 춘천시 춘천로17번길 31 3층 301호,302호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +896,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zpx4</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>O</t>
@@ -906,10 +918,10 @@
         <v>56</v>
       </c>
       <c r="Q5" t="n">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="R5" t="n">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -940,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>고고PT&amp;WOMEN</t>
+          <t>브이핏</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gogo_pt2@naver.com</t>
+          <t>v-fit_official@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1378-2924</t>
+          <t>0507-1354-1394</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강원특별자치도 춘천시 남춘로36번길 20 2층(퇴계동)</t>
+          <t>강원 춘천시 백령로 214 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gogo_pt2</t>
+          <t>https://www.instagram.com/v.fit_v</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,15 +989,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w436zy</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>28</v>
+        <v>147</v>
       </c>
       <c r="Q6" t="n">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="R6" t="n">
-        <v>156</v>
+        <v>207</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1893842305</t>
+          <t>1219020937</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1893842305</t>
+          <t>https://m.place.naver.com/place/1219020937</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>노프짐 춘천점</t>
+          <t>헬스 &amp; PT 굿리프트</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>noffgym@naver.com</t>
+          <t>goodlift_hong@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1305-1277</t>
+          <t>0507-1441-6464</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>강원특별자치도 춘천시 동내면 춘천순환로 63 명일빌딩 3층 노프짐</t>
+          <t>강원 춘천시 효석로 37 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/noffgym</t>
+          <t>https://smartstore.naver.com/goodlift_cc</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,15 +1087,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wpxy8r2</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>168</v>
+        <v>70</v>
       </c>
       <c r="Q7" t="n">
-        <v>147</v>
+        <v>38</v>
       </c>
       <c r="R7" t="n">
-        <v>315</v>
+        <v>108</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1931931002</t>
+          <t>1966374826</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1931931002</t>
+          <t>https://m.place.naver.com/place/1966374826</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1123,34 +1143,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>헬스 &amp; PT 굿리프트</t>
+          <t>엘알엠 트레이닝</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>goodlift_hong@naver.com</t>
+          <t>lrmtraining@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1441-6464</t>
+          <t>0507-1335-2075</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원특별자치도 춘천시 효석로 37 1층</t>
+          <t>강원 춘천시 영서로 2670-1 3층 엘알엠 트레이닝</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/goodlift_cc</t>
+          <t>https://blog.naver.com/lrmtraining</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,15 +1185,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4enem</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="Q8" t="n">
-        <v>38</v>
+        <v>219</v>
       </c>
       <c r="R8" t="n">
-        <v>108</v>
+        <v>257</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1966374826</t>
+          <t>1702068915</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1966374826</t>
+          <t>https://m.place.naver.com/place/1702068915</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1217,34 +1241,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>엘알엠 트레이닝</t>
+          <t>더바디랩PT&amp;필라테스 춘천점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>lrmtraining@naver.com</t>
+          <t>thebodylabcc@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1335-2075</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원특별자치도 춘천시 영서로 2670-1 3층 엘알엠 트레이닝</t>
+          <t>강원 춘천시 퇴계농공로 22 프라임타워 4층 더바디랩PT&amp;필라테스 춘천점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lrmtraining</t>
+          <t>https://blog.naver.com/thebodylabcc/223438996483</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1264,10 +1284,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4g6fm</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1279,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="Q9" t="n">
-        <v>219</v>
+        <v>69</v>
       </c>
       <c r="R9" t="n">
-        <v>257</v>
+        <v>136</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,15 +1318,211 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1702068915</t>
+          <t>1928947972</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1702068915</t>
+          <t>https://m.place.naver.com/place/1928947972</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>코어&amp;밸런스트레이닝센터</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>kth38900@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1341-3855</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>강원 춘천시 행촌로 29 6층</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kth38900</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4269k</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>98</v>
+      </c>
+      <c r="R10" t="n">
+        <v>131</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1045913410</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1045913410</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>미드나잇 짐 온의점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>allow18587@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1421-3525</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>강원 춘천시 춘천로17번길 21 춘천강남하이엔드 2층 206호</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jang_ji_won_/</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41aux</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>53</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1986587948</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1986587948</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/춘천_PT.xlsx
+++ b/naver-place-crawler/results_health/춘천_PT.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -918,10 +918,10 @@
         <v>56</v>
       </c>
       <c r="Q5" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="R5" t="n">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1045,34 +1045,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>헬스 &amp; PT 굿리프트</t>
+          <t>이즈원 필라테스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>goodlift_hong@naver.com</t>
+          <t>napilates-yina@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1441-6464</t>
+          <t>0507-1497-2241</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>강원 춘천시 효석로 37 1층</t>
+          <t>강원 춘천시 영서로 2347-1 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/goodlift_cc</t>
+          <t>https://blog.naver.com/napilates-yina/224230819363</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wpxy8r2</t>
+          <t>https://talk.naver.com/ct/w5vzdd</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="Q7" t="n">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="R7" t="n">
-        <v>108</v>
+        <v>198</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1966374826</t>
+          <t>1888353200</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1966374826</t>
+          <t>https://m.place.naver.com/place/1888353200</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1143,34 +1143,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>엘알엠 트레이닝</t>
+          <t>노프짐 춘천점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lrmtraining@naver.com</t>
+          <t>noffgym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1335-2075</t>
+          <t>0507-1305-1277</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원 춘천시 영서로 2670-1 3층 엘알엠 트레이닝</t>
+          <t>강원 춘천시 동내면 춘천순환로 63 명일빌딩 3층 노프짐</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lrmtraining</t>
+          <t>https://blog.naver.com/noffgym</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4enem</t>
+          <t>https://talk.naver.com/ct/w42pbe</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>38</v>
+        <v>168</v>
       </c>
       <c r="Q8" t="n">
-        <v>219</v>
+        <v>147</v>
       </c>
       <c r="R8" t="n">
-        <v>257</v>
+        <v>315</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1702068915</t>
+          <t>1931931002</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1702068915</t>
+          <t>https://m.place.naver.com/place/1931931002</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1241,30 +1241,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>더바디랩PT&amp;필라테스 춘천점</t>
+          <t>헬스 &amp; PT 굿리프트</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>thebodylabcc@naver.com</t>
+          <t>goodlift_hong@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1441-6464</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원 춘천시 퇴계농공로 22 프라임타워 4층 더바디랩PT&amp;필라테스 춘천점</t>
+          <t>강원 춘천시 효석로 37 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thebodylabcc/223438996483</t>
+          <t>https://smartstore.naver.com/goodlift_cc</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,7 +1283,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1289,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4g6fm</t>
+          <t>https://talk.naver.com/ct/wpxy8r2</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="Q9" t="n">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="R9" t="n">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,211 +1322,15 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1928947972</t>
+          <t>1966374826</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928947972</t>
+          <t>https://m.place.naver.com/place/1966374826</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>코어&amp;밸런스트레이닝센터</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>kth38900@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1341-3855</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>강원 춘천시 행촌로 29 6층</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/kth38900</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4269k</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>98</v>
-      </c>
-      <c r="R10" t="n">
-        <v>131</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1045913410</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1045913410</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>미드나잇 짐 온의점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>allow18587@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1421-3525</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>강원 춘천시 춘천로17번길 21 춘천강남하이엔드 2층 206호</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/jang_ji_won_/</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w41aux</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>52</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>53</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1986587948</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1986587948</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/춘천_PT.xlsx
+++ b/naver-place-crawler/results_health/춘천_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,105 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>엘알엠 트레이닝</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>lrmtraining@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1335-2075</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>강원 춘천시 영서로 2670-1 3층 엘알엠 트레이닝</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/lrmtraining</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4enem</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>219</v>
+      </c>
+      <c r="R10" t="n">
+        <v>257</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1702068915</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1702068915</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/춘천_PT.xlsx
+++ b/naver-place-crawler/results_health/춘천_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="Q3" t="n">
         <v>52</v>
       </c>
       <c r="R3" t="n">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -854,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>아베크짐</t>
+          <t>브이핏</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>wannabe-pt@naver.com</t>
+          <t>v-fit_official@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1340-0660</t>
+          <t>0507-1354-1394</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>강원 춘천시 춘천로17번길 31 3층 301호,302호</t>
+          <t>강원 춘천시 백령로 214 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sFMuVPdh</t>
+          <t>https://www.instagram.com/v.fit_v</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zpx4</t>
+          <t>https://talk.naver.com/ct/w436zy</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>56</v>
+        <v>147</v>
       </c>
       <c r="Q5" t="n">
-        <v>425</v>
+        <v>60</v>
       </c>
       <c r="R5" t="n">
-        <v>481</v>
+        <v>207</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1147379761</t>
+          <t>1219020937</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1147379761</t>
+          <t>https://m.place.naver.com/place/1219020937</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -952,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>브이핏</t>
+          <t>아베크짐</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>v-fit_official@naver.com</t>
+          <t>wannabe-pt@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1354-1394</t>
+          <t>0507-1340-0660</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강원 춘천시 백령로 214 2층</t>
+          <t>강원 춘천시 춘천로17번길 31 3층 301호,302호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/v.fit_v</t>
+          <t>https://open.kakao.com/o/sFMuVPdh</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w436zy</t>
+          <t>https://talk.naver.com/ct/w5zpx4</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>147</v>
+        <v>56</v>
       </c>
       <c r="Q6" t="n">
-        <v>60</v>
+        <v>430</v>
       </c>
       <c r="R6" t="n">
-        <v>207</v>
+        <v>486</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1219020937</t>
+          <t>1147379761</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1219020937</t>
+          <t>https://m.place.naver.com/place/1147379761</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q8" t="n">
         <v>147</v>
       </c>
       <c r="R8" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1331,104 +1331,6 @@
         </is>
       </c>
       <c r="V9" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>엘알엠 트레이닝</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>lrmtraining@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1335-2075</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>강원 춘천시 영서로 2670-1 3층 엘알엠 트레이닝</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/lrmtraining</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4enem</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>219</v>
-      </c>
-      <c r="R10" t="n">
-        <v>257</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1702068915</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1702068915</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/naver-place-crawler/results_health/춘천_PT.xlsx
+++ b/naver-place-crawler/results_health/춘천_PT.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1016,10 +1016,10 @@
         <v>56</v>
       </c>
       <c r="Q6" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="R6" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/춘천_PT.xlsx
+++ b/naver-place-crawler/results_health/춘천_PT.xlsx
@@ -1016,10 +1016,10 @@
         <v>56</v>
       </c>
       <c r="Q6" t="n">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="R6" t="n">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
